--- a/mainWidget/mainWidget/src/database/壳体材料.xlsx
+++ b/mainWidget/mainWidget/src/database/壳体材料.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED737341-9B05-4047-B946-F9CCD1B9F1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4409591F-31A2-44F9-A180-EF659AFC4080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
   <si>
     <r>
       <rPr>
@@ -1141,15 +1141,276 @@
       <t>[GPa]</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>486</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>475</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>345</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>193</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>550</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>515</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>502</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>452</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>862</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>460</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>903</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>155</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>290</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>207</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>71.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>68.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>572</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>879</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>503</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.34</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>255</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>130</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>385</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>117</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>398</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>116</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>245</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>350</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000173</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000117</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000236</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000167</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000122</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000139</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000133</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000264</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000108</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000135</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000234</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000086</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-  </numFmts>
   <fonts count="8">
     <font>
       <sz val="11"/>
@@ -1283,7 +1544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1294,16 +1555,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1312,21 +1564,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1635,7 +1893,9 @@
   <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
-    <col min="5" max="5" width="18.07421875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="11.3046875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="18.07421875" style="13" customWidth="1"/>
+    <col min="6" max="10" width="9.23046875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.45" thickBot="1">
@@ -1648,25 +1908,25 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="9" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1680,26 +1940,26 @@
       <c r="C2" s="3">
         <v>7850</v>
       </c>
-      <c r="D2" s="4">
-        <v>1.2E-5</v>
-      </c>
-      <c r="E2" s="13">
-        <v>200</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="G2" s="3">
-        <v>250</v>
-      </c>
-      <c r="H2" s="3">
+      <c r="D2" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="10">
         <v>475</v>
       </c>
-      <c r="I2" s="3">
-        <v>50.2</v>
-      </c>
-      <c r="J2" s="3">
-        <v>486</v>
+      <c r="I2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="46.75" thickBot="1">
@@ -1712,26 +1972,26 @@
       <c r="C3" s="3">
         <v>7850</v>
       </c>
-      <c r="D3" s="4">
-        <v>1.2E-5</v>
-      </c>
-      <c r="E3" s="13">
-        <v>200</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="G3" s="3">
-        <v>345</v>
-      </c>
-      <c r="H3" s="3">
-        <v>475</v>
-      </c>
-      <c r="I3" s="3">
-        <v>50.2</v>
-      </c>
-      <c r="J3" s="3">
-        <v>486</v>
+      <c r="D3" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.3" thickBot="1">
@@ -1744,26 +2004,26 @@
       <c r="C4" s="3">
         <v>7850</v>
       </c>
-      <c r="D4" s="4">
-        <v>1.2E-5</v>
-      </c>
-      <c r="E4" s="13">
-        <v>200</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="G4" s="3">
-        <v>345</v>
-      </c>
-      <c r="H4" s="3">
-        <v>550</v>
-      </c>
-      <c r="I4" s="3">
-        <v>50.2</v>
-      </c>
-      <c r="J4" s="3">
-        <v>486</v>
+      <c r="D4" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="93.9" thickBot="1">
@@ -1776,26 +2036,26 @@
       <c r="C5" s="3">
         <v>7930</v>
       </c>
-      <c r="D5" s="5">
-        <v>1.73E-5</v>
-      </c>
-      <c r="E5" s="13">
-        <v>193</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="G5" s="3">
-        <v>205</v>
-      </c>
-      <c r="H5" s="3">
-        <v>515</v>
-      </c>
-      <c r="I5" s="3">
-        <v>16.3</v>
-      </c>
-      <c r="J5" s="3">
-        <v>502</v>
+      <c r="D5" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="93.9" thickBot="1">
@@ -1808,26 +2068,26 @@
       <c r="C6" s="3">
         <v>8000</v>
       </c>
-      <c r="D6" s="5">
-        <v>1.5999999999999999E-5</v>
-      </c>
-      <c r="E6" s="13">
-        <v>193</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="G6" s="3">
-        <v>205</v>
-      </c>
-      <c r="H6" s="3">
-        <v>515</v>
-      </c>
-      <c r="I6" s="3">
-        <v>13.7</v>
-      </c>
-      <c r="J6" s="3">
-        <v>452</v>
+      <c r="D6" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="78.45" thickBot="1">
@@ -1840,26 +2100,26 @@
       <c r="C7" s="3">
         <v>7850</v>
       </c>
-      <c r="D7" s="5">
-        <v>1.17E-5</v>
-      </c>
-      <c r="E7" s="13">
-        <v>207</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="G7" s="3">
-        <v>862</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1034</v>
-      </c>
-      <c r="I7" s="3">
-        <v>42.5</v>
-      </c>
-      <c r="J7" s="3">
-        <v>460</v>
+      <c r="D7" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="78.45" thickBot="1">
@@ -1872,26 +2132,26 @@
       <c r="C8" s="3">
         <v>7850</v>
       </c>
-      <c r="D8" s="5">
-        <v>1.2E-5</v>
-      </c>
-      <c r="E8" s="13">
-        <v>200</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="D8" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="10">
         <v>210</v>
       </c>
-      <c r="H8" s="3">
-        <v>400</v>
-      </c>
-      <c r="I8" s="3">
-        <v>50.2</v>
-      </c>
-      <c r="J8" s="3">
-        <v>486</v>
+      <c r="H8" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="63" thickBot="1">
@@ -1904,26 +2164,26 @@
       <c r="C9" s="3">
         <v>2700</v>
       </c>
-      <c r="D9" s="5">
-        <v>2.3600000000000001E-5</v>
-      </c>
-      <c r="E9" s="13">
-        <v>68.900000000000006</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.33</v>
-      </c>
-      <c r="G9" s="3">
-        <v>240</v>
-      </c>
-      <c r="H9" s="3">
-        <v>290</v>
-      </c>
-      <c r="I9" s="3">
-        <v>155</v>
-      </c>
-      <c r="J9" s="3">
-        <v>903</v>
+      <c r="D9" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="63" thickBot="1">
@@ -1936,26 +2196,26 @@
       <c r="C10" s="3">
         <v>2810</v>
       </c>
-      <c r="D10" s="5">
-        <v>2.34E-5</v>
-      </c>
-      <c r="E10" s="13">
-        <v>71.7</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0.33</v>
-      </c>
-      <c r="G10" s="3">
-        <v>503</v>
-      </c>
-      <c r="H10" s="3">
-        <v>572</v>
-      </c>
-      <c r="I10" s="3">
-        <v>130</v>
-      </c>
-      <c r="J10" s="3">
-        <v>879</v>
+      <c r="D10" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="47.15" thickBot="1">
@@ -1968,26 +2228,26 @@
       <c r="C11" s="3">
         <v>8930</v>
       </c>
-      <c r="D11" s="5">
-        <v>1.6699999999999999E-5</v>
-      </c>
-      <c r="E11" s="13">
-        <v>117</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0.34</v>
-      </c>
-      <c r="G11" s="3">
-        <v>90</v>
-      </c>
-      <c r="H11" s="3">
-        <v>255</v>
-      </c>
-      <c r="I11" s="3">
+      <c r="D11" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="10">
         <v>398</v>
       </c>
-      <c r="J11" s="3">
-        <v>385</v>
+      <c r="J11" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="62.6" thickBot="1">
@@ -2000,26 +2260,26 @@
       <c r="C12" s="3">
         <v>8930</v>
       </c>
-      <c r="D12" s="5">
-        <v>1.6699999999999999E-5</v>
-      </c>
-      <c r="E12" s="13">
-        <v>117</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0.34</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="D12" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="10">
         <v>90</v>
       </c>
-      <c r="H12" s="3">
-        <v>255</v>
-      </c>
-      <c r="I12" s="3">
-        <v>398</v>
-      </c>
-      <c r="J12" s="3">
-        <v>385</v>
+      <c r="H12" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="77.599999999999994" thickBot="1">
@@ -2032,26 +2292,26 @@
       <c r="C13" s="3">
         <v>8930</v>
       </c>
-      <c r="D13" s="5">
-        <v>1.6699999999999999E-5</v>
-      </c>
-      <c r="E13" s="13">
-        <v>117</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0.34</v>
-      </c>
-      <c r="G13" s="3">
-        <v>90</v>
-      </c>
-      <c r="H13" s="3">
-        <v>255</v>
-      </c>
-      <c r="I13" s="3">
+      <c r="D13" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="10">
         <v>398</v>
       </c>
-      <c r="J13" s="3">
-        <v>385</v>
+      <c r="J13" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="78.45" thickBot="1">
@@ -2064,26 +2324,26 @@
       <c r="C14" s="3">
         <v>8530</v>
       </c>
-      <c r="D14" s="5">
-        <v>1.9000000000000001E-5</v>
-      </c>
-      <c r="E14" s="13">
-        <v>103</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0.34</v>
-      </c>
-      <c r="G14" s="3">
-        <v>245</v>
-      </c>
-      <c r="H14" s="3">
-        <v>475</v>
-      </c>
-      <c r="I14" s="3">
-        <v>116</v>
-      </c>
-      <c r="J14" s="3">
-        <v>385</v>
+      <c r="D14" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="78.45" thickBot="1">
@@ -2096,505 +2356,505 @@
       <c r="C15" s="3">
         <v>8890</v>
       </c>
-      <c r="D15" s="5">
-        <v>1.7E-5</v>
-      </c>
-      <c r="E15" s="13">
-        <v>110</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0.34</v>
-      </c>
-      <c r="G15" s="3">
-        <v>350</v>
-      </c>
-      <c r="H15" s="3">
-        <v>475</v>
-      </c>
-      <c r="I15" s="3">
-        <v>42.7</v>
-      </c>
-      <c r="J15" s="3">
-        <v>385</v>
+      <c r="D15" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="78.45" thickBot="1">
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="4">
         <v>4430</v>
       </c>
-      <c r="D16" s="7">
-        <v>8.6000000000000007E-6</v>
-      </c>
-      <c r="E16" s="14">
+      <c r="D16" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="F16" s="6">
+      <c r="E16" s="11">
+        <v>103</v>
+      </c>
+      <c r="F16" s="11">
         <v>0.34</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="11">
         <v>827</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="11">
         <v>896</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="11">
         <v>6.7</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="11">
         <v>523</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="47.15" thickBot="1">
-      <c r="A17" s="8">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="6">
         <v>8900</v>
       </c>
-      <c r="D17" s="10">
-        <v>1.33E-5</v>
-      </c>
-      <c r="E17" s="15">
+      <c r="D17" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="12">
         <v>207</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="12">
         <v>0.31</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="12">
         <v>190</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="12">
         <v>420</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="12">
         <v>90.9</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="12">
         <v>444</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="63" thickBot="1">
-      <c r="A18" s="8">
+      <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="6">
         <v>8470</v>
       </c>
-      <c r="D18" s="10">
-        <v>1.2999999999999999E-5</v>
-      </c>
-      <c r="E18" s="15">
+      <c r="D18" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="12">
         <v>203</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="12">
         <v>0.3</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="12">
         <v>248</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="12">
         <v>552</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="12">
         <v>11.3</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="12">
         <v>435</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="63" thickBot="1">
-      <c r="A19" s="8">
+      <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="6">
         <v>8240</v>
       </c>
-      <c r="D19" s="10">
-        <v>1.22E-5</v>
-      </c>
-      <c r="E19" s="15">
+      <c r="D19" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="12">
         <v>207</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="12">
         <v>0.3</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="12">
         <v>1034</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="12">
         <v>1241</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="12">
         <v>11.4</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="12">
         <v>435</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="63" thickBot="1">
-      <c r="A20" s="8">
+      <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="6">
         <v>8900</v>
       </c>
-      <c r="D20" s="10">
-        <v>1.03E-5</v>
-      </c>
-      <c r="E20" s="15">
+      <c r="D20" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" s="12">
         <v>210</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="12">
         <v>0.3</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="12">
         <v>414</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="12">
         <v>793</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="12">
         <v>9.8000000000000007</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="12">
         <v>427</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="63" thickBot="1">
-      <c r="A21" s="8">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="6">
         <v>8800</v>
       </c>
-      <c r="D21" s="10">
-        <v>1.3900000000000001E-5</v>
-      </c>
-      <c r="E21" s="15">
+      <c r="D21" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="12">
         <v>186</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="12">
         <v>0.32</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="12">
         <v>248</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="12">
         <v>517</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="12">
         <v>21.5</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="12">
         <v>427</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="78" thickBot="1">
-      <c r="A22" s="8">
+      <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="6">
         <v>7200</v>
       </c>
-      <c r="D22" s="10">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="E22" s="15">
+      <c r="D22" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="12">
         <v>103</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="12">
         <v>0.27</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="12">
         <v>440</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="12">
         <v>207</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="12">
         <v>46.5</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="12">
         <v>460</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="93" thickBot="1">
-      <c r="A23" s="8">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="6">
         <v>7100</v>
       </c>
-      <c r="D23" s="10">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="E23" s="15">
+      <c r="D23" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="12">
         <v>169</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="12">
         <v>0.28000000000000003</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="12">
         <v>448</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="12">
         <v>448</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="12">
         <v>46.5</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="12">
         <v>460</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="47.15" thickBot="1">
-      <c r="A24" s="8">
+      <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="6">
         <v>1740</v>
       </c>
-      <c r="D24" s="10">
-        <v>2.5999999999999998E-5</v>
-      </c>
-      <c r="E24" s="15">
+      <c r="D24" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="12">
         <v>448</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="12">
         <v>0.35</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="12">
         <v>200</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="12">
         <v>270</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="12">
         <v>156</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="12">
         <v>1025</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="78" thickBot="1">
-      <c r="A25" s="8">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="6">
         <v>6660</v>
       </c>
-      <c r="D25" s="10">
-        <v>2.6400000000000001E-5</v>
-      </c>
-      <c r="E25" s="15">
+      <c r="D25" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25" s="12">
         <v>38</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="12">
         <v>0.27</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="12">
         <v>248</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="12">
         <v>324</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="12">
         <v>113</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="12">
         <v>388</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="77.599999999999994" thickBot="1">
-      <c r="A26" s="8">
+      <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="6">
         <v>7850</v>
       </c>
-      <c r="D26" s="10">
-        <v>1.1E-5</v>
-      </c>
-      <c r="E26" s="15">
+      <c r="D26" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="12">
         <v>200</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="12">
         <v>0.3</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="12">
         <v>205</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="12">
         <v>415</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="12">
         <v>36.4</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="12">
         <v>460</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="77.599999999999994" thickBot="1">
-      <c r="A27" s="8">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="6">
         <v>7850</v>
       </c>
-      <c r="D27" s="10">
-        <v>1.08E-5</v>
-      </c>
-      <c r="E27" s="15">
+      <c r="D27" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="12">
         <v>200</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="12">
         <v>0.3</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="12">
         <v>170</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="12">
         <v>415</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="12">
         <v>30.9</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="12">
         <v>460</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="93" thickBot="1">
-      <c r="A28" s="8">
+      <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="6">
         <v>7750</v>
       </c>
-      <c r="D28" s="10">
-        <v>1.04E-5</v>
-      </c>
-      <c r="E28" s="15">
+      <c r="D28" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="12">
         <v>200</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="12">
         <v>0.3</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="12">
         <v>205</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="12">
         <v>448</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="12">
         <v>26</v>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="12">
         <v>460</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="92.15" thickBot="1">
-      <c r="A29" s="8">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="6">
         <v>7800</v>
       </c>
-      <c r="D29" s="10">
-        <v>1.3499999999999999E-5</v>
-      </c>
-      <c r="E29" s="15">
+      <c r="D29" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" s="12">
         <v>200</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="12">
         <v>0.3</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="12">
         <v>450</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="12">
         <v>620</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="12">
         <v>18</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="12">
         <v>452</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="92.6" thickBot="1">
-      <c r="A30" s="8">
+      <c r="A30" s="5">
         <v>29</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="6">
         <v>7780</v>
       </c>
-      <c r="D30" s="10">
-        <v>1.04E-5</v>
-      </c>
-      <c r="E30" s="15">
+      <c r="D30" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" s="12">
         <v>200</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="12">
         <v>0.3</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="12">
         <v>1100</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="12">
         <v>1240</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="12">
         <v>16.3</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="12">
         <v>460</v>
       </c>
     </row>

--- a/mainWidget/mainWidget/src/database/壳体材料.xlsx
+++ b/mainWidget/mainWidget/src/database/壳体材料.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4409591F-31A2-44F9-A180-EF659AFC4080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="116">
   <si>
     <r>
       <rPr>
@@ -1119,6 +1113,238 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>486</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>475</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>345</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>550</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>515</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>502</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>452</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>862</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>460</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>903</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>155</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>290</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>572</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>879</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>503</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.34</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>255</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>130</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>385</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>398</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>116</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>245</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>350</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000173</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000117</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000236</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000167</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000122</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000139</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000133</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000264</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000108</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000135</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000234</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000086</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1138,280 +1364,92 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>[GPa]</t>
+      <t>[MPa]</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>50.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>486</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>475</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>345</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>193</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>205</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>550</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>515</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>502</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>452</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>862</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1034</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>42.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>460</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>903</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>155</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>290</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>240</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.33</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>207</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>71.7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>68.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>572</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>879</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>503</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.34</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>255</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>130</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>385</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>117</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>398</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>110</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>116</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>245</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>350</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>42.7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000173</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000117</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000236</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000167</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000122</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000139</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000133</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000264</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000108</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000135</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000234</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000086</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000013</t>
+    <t>200000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>193000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>207000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>68900000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>71700000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>117000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>117000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>103000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>103000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>207000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>203000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>210000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>186000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>169000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>448000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200000000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1604,9 +1642,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1644,7 +1682,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1716,7 +1754,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1889,16 +1927,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="4" max="4" width="11.3046875" style="13" customWidth="1"/>
     <col min="5" max="5" width="18.07421875" style="13" customWidth="1"/>
     <col min="6" max="10" width="9.23046875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.45" thickBot="1">
+    <row r="1" spans="1:10" ht="15.45" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1912,7 +1950,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>4</v>
@@ -1930,7 +1968,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="31.3" thickBot="1">
+    <row r="2" spans="1:10" ht="31.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1941,28 +1979,28 @@
         <v>7850</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E2" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>39</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>41</v>
       </c>
       <c r="H2" s="10">
         <v>475</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="46.75" thickBot="1">
+    <row r="3" spans="1:10" ht="46.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1973,28 +2011,28 @@
         <v>7850</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="F3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="J3" s="10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="31.3" thickBot="1">
+    <row r="4" spans="1:10" ht="31.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2005,28 +2043,28 @@
         <v>7850</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="F4" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="J4" s="10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="93.9" thickBot="1">
+    <row r="5" spans="1:10" ht="93.9" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2037,28 +2075,28 @@
         <v>7930</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E5" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="10" t="s">
+      <c r="I5" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>50</v>
-      </c>
       <c r="J5" s="10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="93.9" thickBot="1">
+    <row r="6" spans="1:10" ht="93.9" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2069,28 +2107,28 @@
         <v>8000</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E6" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="10" t="s">
+      <c r="I6" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>52</v>
-      </c>
     </row>
-    <row r="7" spans="1:10" ht="78.45" thickBot="1">
+    <row r="7" spans="1:10" ht="78.45" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2101,28 +2139,28 @@
         <v>7850</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G7" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>57</v>
-      </c>
     </row>
-    <row r="8" spans="1:10" ht="78.45" thickBot="1">
+    <row r="8" spans="1:10" ht="78.45" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2133,28 +2171,28 @@
         <v>7850</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G8" s="10">
         <v>210</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="63" thickBot="1">
+    <row r="9" spans="1:10" ht="63" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2165,28 +2203,28 @@
         <v>2700</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="63" thickBot="1">
+    <row r="10" spans="1:10" ht="63" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2197,28 +2235,28 @@
         <v>2810</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="F10" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="H10" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="10" t="s">
-        <v>73</v>
-      </c>
       <c r="J10" s="10" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="47.15" thickBot="1">
+    <row r="11" spans="1:10" ht="47.15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2229,28 +2267,28 @@
         <v>8930</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I11" s="10">
         <v>398</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="62.6" thickBot="1">
+    <row r="12" spans="1:10" ht="62.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2261,28 +2299,28 @@
         <v>8930</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G12" s="10">
         <v>90</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="77.599999999999994" thickBot="1">
+    <row r="13" spans="1:10" ht="77.599999999999994" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2293,28 +2331,28 @@
         <v>8930</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I13" s="10">
         <v>398</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="78.45" thickBot="1">
+    <row r="14" spans="1:10" ht="78.45" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2325,28 +2363,28 @@
         <v>8530</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="F14" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>79</v>
-      </c>
       <c r="J14" s="10" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="78.45" thickBot="1">
+    <row r="15" spans="1:10" ht="78.45" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2357,28 +2395,28 @@
         <v>8890</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="78.45" thickBot="1">
+    <row r="16" spans="1:10" ht="78.45" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -2389,10 +2427,10 @@
         <v>4430</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" s="11">
-        <v>103</v>
+        <v>94</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="F16" s="11">
         <v>0.34</v>
@@ -2410,7 +2448,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="47.15" thickBot="1">
+    <row r="17" spans="1:10" ht="47.15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -2421,10 +2459,10 @@
         <v>8900</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="12">
-        <v>207</v>
+        <v>84</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="F17" s="12">
         <v>0.31</v>
@@ -2442,7 +2480,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="63" thickBot="1">
+    <row r="18" spans="1:10" ht="63" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -2453,10 +2491,10 @@
         <v>8470</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18" s="12">
-        <v>203</v>
+        <v>95</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="F18" s="12">
         <v>0.3</v>
@@ -2474,7 +2512,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="63" thickBot="1">
+    <row r="19" spans="1:10" ht="63" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -2485,10 +2523,10 @@
         <v>8240</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" s="12">
-        <v>207</v>
+        <v>80</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="F19" s="12">
         <v>0.3</v>
@@ -2506,7 +2544,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="63" thickBot="1">
+    <row r="20" spans="1:10" ht="63" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -2517,10 +2555,10 @@
         <v>8900</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="12">
-        <v>210</v>
+        <v>81</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>110</v>
       </c>
       <c r="F20" s="12">
         <v>0.3</v>
@@ -2538,7 +2576,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="63" thickBot="1">
+    <row r="21" spans="1:10" ht="63" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -2549,10 +2587,10 @@
         <v>8800</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="12">
-        <v>186</v>
+        <v>82</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="F21" s="12">
         <v>0.32</v>
@@ -2570,7 +2608,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="78" thickBot="1">
+    <row r="22" spans="1:10" ht="78" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -2581,10 +2619,10 @@
         <v>7200</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E22" s="12">
-        <v>103</v>
+        <v>83</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="F22" s="12">
         <v>0.27</v>
@@ -2602,7 +2640,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="93" thickBot="1">
+    <row r="23" spans="1:10" ht="93" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -2613,10 +2651,10 @@
         <v>7100</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="12">
-        <v>169</v>
+        <v>83</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>112</v>
       </c>
       <c r="F23" s="12">
         <v>0.28000000000000003</v>
@@ -2634,7 +2672,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="47.15" thickBot="1">
+    <row r="24" spans="1:10" ht="47.15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -2645,10 +2683,10 @@
         <v>1740</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" s="12">
-        <v>448</v>
+        <v>87</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>113</v>
       </c>
       <c r="F24" s="12">
         <v>0.35</v>
@@ -2666,7 +2704,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="78" thickBot="1">
+    <row r="25" spans="1:10" ht="78" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -2677,10 +2715,10 @@
         <v>6660</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E25" s="12">
-        <v>38</v>
+        <v>86</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="F25" s="12">
         <v>0.27</v>
@@ -2698,7 +2736,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="77.599999999999994" thickBot="1">
+    <row r="26" spans="1:10" ht="77.599999999999994" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -2709,10 +2747,10 @@
         <v>7850</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" s="12">
-        <v>200</v>
+        <v>85</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="F26" s="12">
         <v>0.3</v>
@@ -2730,7 +2768,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="77.599999999999994" thickBot="1">
+    <row r="27" spans="1:10" ht="77.599999999999994" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -2741,10 +2779,10 @@
         <v>7850</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E27" s="12">
-        <v>200</v>
+        <v>88</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="F27" s="12">
         <v>0.3</v>
@@ -2762,7 +2800,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="93" thickBot="1">
+    <row r="28" spans="1:10" ht="93" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -2773,10 +2811,10 @@
         <v>7750</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" s="12">
-        <v>200</v>
+        <v>89</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="F28" s="12">
         <v>0.3</v>
@@ -2794,7 +2832,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="92.15" thickBot="1">
+    <row r="29" spans="1:10" ht="92.15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -2805,10 +2843,10 @@
         <v>7800</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E29" s="12">
-        <v>200</v>
+        <v>90</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="F29" s="12">
         <v>0.3</v>
@@ -2826,7 +2864,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="92.6" thickBot="1">
+    <row r="30" spans="1:10" ht="92.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -2837,10 +2875,10 @@
         <v>7780</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" s="12">
-        <v>200</v>
+        <v>89</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="F30" s="12">
         <v>0.3</v>
